--- a/artefakti/s04-risk/FinanceGroup-JSC_risk.xlsx
+++ b/artefakti/s04-risk/FinanceGroup-JSC_risk.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="410">
   <si>
     <t xml:space="preserve">МИС — инструмент за риска (инвентаризация, оценка на риска, план за третиране)</t>
   </si>
@@ -451,7 +451,7 @@
     <t xml:space="preserve">Identity-aware прокси (oauth2-proxy)</t>
   </si>
   <si>
-    <t xml:space="preserve">Чувствителното приложение е зад проксито (урок 11)</t>
+    <t xml:space="preserve">Чувствителното приложение е зад проксито </t>
   </si>
   <si>
     <t xml:space="preserve">A-05</t>
@@ -460,7 +460,7 @@
     <t xml:space="preserve">Keycloak — идентичности и роли (8443)</t>
   </si>
   <si>
-    <t xml:space="preserve">Роли: одитор (пълен достъп), клонов служител (само портал) — урок 7</t>
+    <t xml:space="preserve">Роли: одитор (пълен достъп), клонов служител (само портал)</t>
   </si>
   <si>
     <t xml:space="preserve">A-06</t>
@@ -562,7 +562,7 @@
     <t xml:space="preserve">LAN-HQ, хост mon</t>
   </si>
   <si>
-    <t xml:space="preserve">Обект за наблюдение — уроци 13, 14</t>
+    <t xml:space="preserve">Обект за наблюдение</t>
   </si>
   <si>
     <t xml:space="preserve">A-13</t>
@@ -955,9 +955,6 @@
     <t xml:space="preserve">планиран</t>
   </si>
   <si>
-    <t xml:space="preserve">artefakti/h11-proxy/, artefakti/h09-nftables/ (планирано)</t>
-  </si>
-  <si>
     <t xml:space="preserve">-*J13,J11,J1</t>
   </si>
   <si>
@@ -967,36 +964,24 @@
     <t xml:space="preserve">M1032: MFA (TOTP) за всички роли, задължително за одитори; M1027 + M1036: политика за пароли и временно заключване при грешни опити в Keycloak; M1018: преглед и премахване на неизползвани акаунти</t>
   </si>
   <si>
-    <t xml:space="preserve">artefakti/h07-keycloak/ (планирано)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Фишинг на одитор и изнасяне на данни към облачно хранилище</t>
   </si>
   <si>
     <t xml:space="preserve">M1017: обучение за фишинг на одиторите; M1049 + M1021: антималуер и уеб филтриране на HQ станциите; M1057: контрол върху качване към облачни хранилища (изходящ nftables филтър); M1032: MFA срещу ползване на откраднати пароли</t>
   </si>
   <si>
-    <t xml:space="preserve">artefakti/h07-keycloak/, artefakti/h13-wazuh/ (планирано)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ransomware върху счетоводните данни и резервните копия</t>
   </si>
   <si>
     <t xml:space="preserve">M1053: изолирано (offline/immutable) резервно копие по 3-2-1 с тест за възстановяване; M1040: поведенческа защита срещу масово криптиране + Wazuh FIM правила; M1030 + M1018: ограничаване на достъпа до сървъра</t>
   </si>
   <si>
-    <t xml:space="preserve">artefakti/h09-nftables/, artefakti/h13-wazuh/ (планирано)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Тихо изменение на счетоводни записи</t>
   </si>
   <si>
     <t xml:space="preserve">M1022: минимални права за запис; M1041: криптиране на чувствителните данни; M1029: неизменяемо резервно копие и версии за сравнение; Wazuh FIM върху данните (откриване по ATT&amp;CK DET0193)</t>
   </si>
   <si>
-    <t xml:space="preserve">artefakti/h03-dani/, artefakti/h13-wazuh/ (планирано)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Изключване или промяна на защитната стена gw</t>
   </si>
   <si>
@@ -1015,27 +1000,18 @@
     <t xml:space="preserve">приет</t>
   </si>
   <si>
-    <t xml:space="preserve">Приема: Управител, 13.10.2026; обхватът е ограничен от nftables</t>
-  </si>
-  <si>
     <t xml:space="preserve">Изтриване на локални журнали от нападател</t>
   </si>
   <si>
     <t xml:space="preserve">— (съществуващ контрол: M1029 — логовете се препращат към mon)</t>
   </si>
   <si>
-    <t xml:space="preserve">Приема: Управител, 13.10.2026; следи се от Wazuh</t>
-  </si>
-  <si>
     <t xml:space="preserve">Достъп до сървъра от компрометирана HQ станция</t>
   </si>
   <si>
     <t xml:space="preserve">M1035 + M1030: SSH само от админ станция (jump host) и достъп на одиторите само до нужните портове; M1032: ключове и MFA за SSH; изходящ филтър на srv</t>
   </si>
   <si>
-    <t xml:space="preserve">artefakti/h09-nftables/ (планирано)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Измамно плащане чрез променени банкови данни</t>
   </si>
   <si>
@@ -1048,9 +1024,6 @@
     <t xml:space="preserve">— (съществуващ контрол: M1030 — forward DROP и забрана на P2P)</t>
   </si>
   <si>
-    <t xml:space="preserve">Приема: Ръководител ИТ, 13.10.2026; тест на правилото в урок 9</t>
-  </si>
-  <si>
     <t xml:space="preserve">Фишинг на единствения системен администратор</t>
   </si>
   <si>
@@ -1061,9 +1034,6 @@
   </si>
   <si>
     <t xml:space="preserve">— (по желание: M1034 + M1035 — забрана на непознати устройства и изключване на неизползвани портове)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Приема: Управител, 13.10.2026; следващ преглед при промяна на офиса</t>
   </si>
   <si>
     <t xml:space="preserve">Как са определени вероятността (P) и въздействието (I) — по MITRE ATT&amp;CK</t>
@@ -1677,7 +1647,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -12390,19 +12360,17 @@
         <f aca="false">IF(OR(L2="",M2=""),"",L2*M2)</f>
         <v>8</v>
       </c>
-      <c r="O2" s="18" t="s">
-        <v>283</v>
-      </c>
+      <c r="O2" s="18"/>
     </row>
     <row r="3" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>116</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D3" s="20" t="str">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A3,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12412,7 +12380,7 @@
         <v>194</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="17" t="s">
@@ -12435,9 +12403,7 @@
         <f aca="false">IF(OR(L3="",M3=""),"",L3*M3)</f>
         <v>8</v>
       </c>
-      <c r="O3" s="18" t="s">
-        <v>287</v>
-      </c>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
@@ -12447,7 +12413,7 @@
         <v>157</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D4" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A4,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12457,7 +12423,7 @@
         <v>194</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="17" t="s">
@@ -12480,9 +12446,7 @@
         <f aca="false">IF(OR(L4="",M4=""),"",L4*M4)</f>
         <v>9</v>
       </c>
-      <c r="O4" s="17" t="s">
-        <v>290</v>
-      </c>
+      <c r="O4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
@@ -12492,7 +12456,7 @@
         <v>103</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D5" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A5,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12502,7 +12466,7 @@
         <v>194</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="17" t="s">
@@ -12525,9 +12489,7 @@
         <f aca="false">IF(OR(L5="",M5=""),"",L5*M5)</f>
         <v>9</v>
       </c>
-      <c r="O5" s="17" t="s">
-        <v>293</v>
-      </c>
+      <c r="O5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
@@ -12537,7 +12499,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D6" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A6,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12547,7 +12509,7 @@
         <v>194</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17" t="s">
@@ -12570,9 +12532,7 @@
         <f aca="false">IF(OR(L6="",M6=""),"",L6*M6)</f>
         <v>6</v>
       </c>
-      <c r="O6" s="17" t="s">
-        <v>296</v>
-      </c>
+      <c r="O6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
@@ -12582,7 +12542,7 @@
         <v>124</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D7" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A7,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12592,7 +12552,7 @@
         <v>194</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="17" t="s">
@@ -12615,9 +12575,7 @@
         <f aca="false">IF(OR(L7="",M7=""),"",L7*M7)</f>
         <v>8</v>
       </c>
-      <c r="O7" s="17" t="s">
-        <v>293</v>
-      </c>
+      <c r="O7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="17" t="s">
@@ -12627,7 +12585,7 @@
         <v>140</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D8" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A8,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12637,18 +12595,18 @@
         <v>232</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="17" t="s">
         <v>110</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="17" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L8" s="17" t="n">
         <v>2</v>
@@ -12660,9 +12618,7 @@
         <f aca="false">IF(OR(L8="",M8=""),"",L8*M8)</f>
         <v>8</v>
       </c>
-      <c r="O8" s="17" t="s">
-        <v>303</v>
-      </c>
+      <c r="O8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
@@ -12672,7 +12628,7 @@
         <v>153</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D9" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A9,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12682,7 +12638,7 @@
         <v>232</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17" t="s">
@@ -12691,7 +12647,7 @@
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
       <c r="K9" s="17" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L9" s="17" t="n">
         <v>3</v>
@@ -12703,9 +12659,7 @@
         <f aca="false">IF(OR(L9="",M9=""),"",L9*M9)</f>
         <v>9</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>306</v>
-      </c>
+      <c r="O9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
@@ -12715,7 +12669,7 @@
         <v>119</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="D10" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A10,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12725,7 +12679,7 @@
         <v>194</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="17" t="s">
@@ -12748,9 +12702,7 @@
         <f aca="false">IF(OR(L10="",M10=""),"",L10*M10)</f>
         <v>8</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>309</v>
-      </c>
+      <c r="O10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="17" t="s">
@@ -12760,7 +12712,7 @@
         <v>95</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A11,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12770,7 +12722,7 @@
         <v>194</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="17" t="s">
@@ -12793,9 +12745,7 @@
         <f aca="false">IF(OR(L11="",M11=""),"",L11*M11)</f>
         <v>6</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>287</v>
-      </c>
+      <c r="O11" s="17"/>
     </row>
     <row r="12" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="17" t="s">
@@ -12805,7 +12755,7 @@
         <v>129</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D12" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A12,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12815,7 +12765,7 @@
         <v>232</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="17" t="s">
@@ -12828,7 +12778,7 @@
         <v>160</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L12" s="17" t="n">
         <v>2</v>
@@ -12840,9 +12790,7 @@
         <f aca="false">IF(OR(L12="",M12=""),"",L12*M12)</f>
         <v>8</v>
       </c>
-      <c r="O12" s="17" t="s">
-        <v>314</v>
-      </c>
+      <c r="O12" s="17"/>
     </row>
     <row r="13" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
@@ -12852,7 +12800,7 @@
         <v>162</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="D13" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A13,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12862,7 +12810,7 @@
         <v>194</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="G13" s="17"/>
       <c r="H13" s="17" t="s">
@@ -12885,9 +12833,7 @@
         <f aca="false">IF(OR(L13="",M13=""),"",L13*M13)</f>
         <v>6</v>
       </c>
-      <c r="O13" s="17" t="s">
-        <v>290</v>
-      </c>
+      <c r="O13" s="17"/>
     </row>
     <row r="14" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="17" t="s">
@@ -12897,7 +12843,7 @@
         <v>166</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D14" s="20" t="n">
         <f aca="false">IFERROR(INDEX('Регистър на риска'!$I:$I,MATCH(A14,'Регистър на риска'!$A:$A,0)),"")</f>
@@ -12907,7 +12853,7 @@
         <v>232</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="17" t="s">
@@ -12920,7 +12866,7 @@
         <v>160</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L14" s="17" t="n">
         <v>2</v>
@@ -12932,9 +12878,7 @@
         <f aca="false">IF(OR(L14="",M14=""),"",L14*M14)</f>
         <v>6</v>
       </c>
-      <c r="O14" s="17" t="s">
-        <v>319</v>
-      </c>
+      <c r="O14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17"/>
@@ -17440,25 +17384,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="22" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>177</v>
@@ -17469,7 +17413,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">A6+1</f>
@@ -17481,7 +17425,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C7" s="25" t="n">
         <f aca="false">A7+1</f>
@@ -17493,7 +17437,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="C8" s="25" t="n">
         <f aca="false">A8+1</f>
@@ -17505,7 +17449,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">A9+1</f>
@@ -17514,25 +17458,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B15" s="25" t="n">
         <v>2</v>
@@ -17540,7 +17484,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B16" s="25" t="n">
         <v>3</v>
@@ -17548,7 +17492,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B17" s="25" t="n">
         <v>4</v>
@@ -17556,7 +17500,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B18" s="25" t="n">
         <v>5</v>
@@ -17564,12 +17508,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="22" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17577,43 +17521,43 @@
         <v>171</v>
       </c>
       <c r="B22" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>331</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>334</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>336</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>337</v>
+      </c>
+      <c r="M22" s="24" t="s">
+        <v>338</v>
+      </c>
+      <c r="N22" s="24" t="s">
         <v>339</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>323</v>
-      </c>
-      <c r="E22" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="G22" s="24" t="s">
-        <v>343</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>346</v>
-      </c>
-      <c r="L22" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="N22" s="24" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17621,10 +17565,10 @@
         <v>188</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D23" s="26" t="n">
         <v>4</v>
@@ -17634,7 +17578,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="G23" s="27" t="n">
         <f aca="false">LEN(F23)-LEN(SUBSTITUTE(F23,",",""))+1</f>
@@ -17648,7 +17592,7 @@
         <v>-2</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="K23" s="27" t="n">
         <f aca="false">MAX(1,H23+I23)</f>
@@ -17659,10 +17603,10 @@
         <v>да</v>
       </c>
       <c r="M23" s="25" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="N23" s="25" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17670,10 +17614,10 @@
         <v>196</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D24" s="26" t="n">
         <v>3</v>
@@ -17683,7 +17627,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G24" s="27" t="n">
         <f aca="false">LEN(F24)-LEN(SUBSTITUTE(F24,",",""))+1</f>
@@ -17697,7 +17641,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="25" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="K24" s="27" t="n">
         <f aca="false">MAX(1,H24+I24)</f>
@@ -17708,10 +17652,10 @@
         <v>да</v>
       </c>
       <c r="M24" s="25" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="N24" s="25" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17719,10 +17663,10 @@
         <v>203</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="D25" s="26" t="n">
         <v>4</v>
@@ -17732,7 +17676,7 @@
         <v>5</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="G25" s="27" t="n">
         <f aca="false">LEN(F25)-LEN(SUBSTITUTE(F25,",",""))+1</f>
@@ -17746,7 +17690,7 @@
         <v>-1</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="K25" s="27" t="n">
         <f aca="false">MAX(1,H25+I25)</f>
@@ -17757,10 +17701,10 @@
         <v>да</v>
       </c>
       <c r="M25" s="25" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="N25" s="25" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17768,10 +17712,10 @@
         <v>209</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D26" s="26" t="n">
         <v>4</v>
@@ -17781,7 +17725,7 @@
         <v>5</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="G26" s="27" t="n">
         <f aca="false">LEN(F26)-LEN(SUBSTITUTE(F26,",",""))+1</f>
@@ -17795,7 +17739,7 @@
         <v>0</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="K26" s="27" t="n">
         <f aca="false">MAX(1,H26+I26)</f>
@@ -17806,10 +17750,10 @@
         <v>да</v>
       </c>
       <c r="M26" s="25" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="N26" s="25" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17817,10 +17761,10 @@
         <v>215</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D27" s="26" t="n">
         <v>4</v>
@@ -17830,7 +17774,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="G27" s="27" t="n">
         <f aca="false">LEN(F27)-LEN(SUBSTITUTE(F27,",",""))+1</f>
@@ -17844,7 +17788,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="K27" s="27" t="n">
         <f aca="false">MAX(1,H27+I27)</f>
@@ -17855,10 +17799,10 @@
         <v>да</v>
       </c>
       <c r="M27" s="25" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="N27" s="25" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17866,10 +17810,10 @@
         <v>220</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D28" s="26" t="n">
         <v>3</v>
@@ -17879,7 +17823,7 @@
         <v>4</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G28" s="27" t="n">
         <f aca="false">LEN(F28)-LEN(SUBSTITUTE(F28,",",""))+1</f>
@@ -17893,7 +17837,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="K28" s="27" t="n">
         <f aca="false">MAX(1,H28+I28)</f>
@@ -17904,10 +17848,10 @@
         <v>да</v>
       </c>
       <c r="M28" s="25" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="N28" s="25" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17915,10 +17859,10 @@
         <v>226</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D29" s="26" t="n">
         <v>3</v>
@@ -17928,7 +17872,7 @@
         <v>4</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="G29" s="27" t="n">
         <f aca="false">LEN(F29)-LEN(SUBSTITUTE(F29,",",""))+1</f>
@@ -17942,7 +17886,7 @@
         <v>-1</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="K29" s="27" t="n">
         <f aca="false">MAX(1,H29+I29)</f>
@@ -17953,10 +17897,10 @@
         <v>да</v>
       </c>
       <c r="M29" s="25" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="N29" s="25" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17964,10 +17908,10 @@
         <v>233</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="D30" s="26" t="n">
         <v>2</v>
@@ -17977,7 +17921,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="G30" s="27" t="n">
         <f aca="false">LEN(F30)-LEN(SUBSTITUTE(F30,",",""))+1</f>
@@ -17991,7 +17935,7 @@
         <v>-1</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="K30" s="27" t="n">
         <f aca="false">MAX(1,H30+I30)</f>
@@ -18002,10 +17946,10 @@
         <v>да</v>
       </c>
       <c r="M30" s="25" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="N30" s="25" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18013,10 +17957,10 @@
         <v>239</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D31" s="26" t="n">
         <v>4</v>
@@ -18026,7 +17970,7 @@
         <v>5</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G31" s="27" t="n">
         <f aca="false">LEN(F31)-LEN(SUBSTITUTE(F31,",",""))+1</f>
@@ -18040,7 +17984,7 @@
         <v>-1</v>
       </c>
       <c r="J31" s="25" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="K31" s="27" t="n">
         <f aca="false">MAX(1,H31+I31)</f>
@@ -18051,10 +17995,10 @@
         <v>да</v>
       </c>
       <c r="M31" s="25" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="N31" s="25" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18062,10 +18006,10 @@
         <v>245</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D32" s="26" t="n">
         <v>4</v>
@@ -18075,7 +18019,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G32" s="27" t="n">
         <f aca="false">LEN(F32)-LEN(SUBSTITUTE(F32,",",""))+1</f>
@@ -18089,7 +18033,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="K32" s="27" t="n">
         <f aca="false">MAX(1,H32+I32)</f>
@@ -18100,10 +18044,10 @@
         <v>да</v>
       </c>
       <c r="M32" s="25" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="N32" s="25" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18111,10 +18055,10 @@
         <v>251</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D33" s="26" t="n">
         <v>3</v>
@@ -18124,7 +18068,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="G33" s="27" t="n">
         <f aca="false">LEN(F33)-LEN(SUBSTITUTE(F33,",",""))+1</f>
@@ -18138,7 +18082,7 @@
         <v>-1</v>
       </c>
       <c r="J33" s="25" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="K33" s="27" t="n">
         <f aca="false">MAX(1,H33+I33)</f>
@@ -18149,10 +18093,10 @@
         <v>да</v>
       </c>
       <c r="M33" s="25" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="N33" s="25" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18160,10 +18104,10 @@
         <v>257</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="D34" s="26" t="n">
         <v>3</v>
@@ -18173,7 +18117,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="G34" s="27" t="n">
         <f aca="false">LEN(F34)-LEN(SUBSTITUTE(F34,",",""))+1</f>
@@ -18187,7 +18131,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="25" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="K34" s="27" t="n">
         <f aca="false">MAX(1,H34+I34)</f>
@@ -18198,10 +18142,10 @@
         <v>да</v>
       </c>
       <c r="M34" s="25" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="N34" s="25" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="78" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18209,10 +18153,10 @@
         <v>263</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D35" s="26" t="n">
         <v>2</v>
@@ -18222,7 +18166,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="G35" s="27" t="n">
         <f aca="false">LEN(F35)-LEN(SUBSTITUTE(F35,",",""))+1</f>
@@ -18236,7 +18180,7 @@
         <v>0</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="K35" s="27" t="n">
         <f aca="false">MAX(1,H35+I35)</f>
@@ -18247,15 +18191,15 @@
         <v>да</v>
       </c>
       <c r="M35" s="25" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="N35" s="25" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="22" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
     </row>
   </sheetData>
